--- a/A 题/result2.xlsx
+++ b/A 题/result2.xlsx
@@ -562,19 +562,19 @@
         <v>28</v>
       </c>
       <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>52</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
@@ -701,27 +701,30 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>34</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>35</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>36</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>49</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>22</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>23</v>
       </c>
     </row>
@@ -733,58 +736,55 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1869,7 +1869,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -1958,7 +1958,7 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
         <v>81</v>
@@ -2721,13 +2721,13 @@
         <v>122</v>
       </c>
       <c r="AE3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>47</v>
+      </c>
+      <c r="AG3" t="n">
         <v>23</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>47</v>
       </c>
       <c r="AH3" t="n">
         <v>40</v>
@@ -2789,124 +2789,124 @@
         <v>88</v>
       </c>
       <c r="C4" t="n">
+        <v>124</v>
+      </c>
+      <c r="D4" t="n">
+        <v>129</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>85</v>
+      </c>
+      <c r="J4" t="n">
+        <v>90</v>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>83</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>81</v>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" t="n">
+        <v>87</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>73</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74</v>
+      </c>
+      <c r="W4" t="n">
+        <v>75</v>
+      </c>
+      <c r="X4" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>111</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>123</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>101</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>119</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>113</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>89</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>98</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP4" t="n">
         <v>26</v>
-      </c>
-      <c r="D4" t="n">
-        <v>97</v>
-      </c>
-      <c r="E4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>98</v>
-      </c>
-      <c r="H4" t="n">
-        <v>89</v>
-      </c>
-      <c r="I4" t="n">
-        <v>113</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" t="n">
-        <v>36</v>
-      </c>
-      <c r="L4" t="n">
-        <v>84</v>
-      </c>
-      <c r="M4" t="n">
-        <v>119</v>
-      </c>
-      <c r="N4" t="n">
-        <v>101</v>
-      </c>
-      <c r="O4" t="n">
-        <v>123</v>
-      </c>
-      <c r="P4" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>101</v>
-      </c>
-      <c r="R4" t="n">
-        <v>82</v>
-      </c>
-      <c r="S4" t="n">
-        <v>57</v>
-      </c>
-      <c r="T4" t="n">
-        <v>9</v>
-      </c>
-      <c r="U4" t="n">
-        <v>52</v>
-      </c>
-      <c r="V4" t="n">
-        <v>75</v>
-      </c>
-      <c r="W4" t="n">
-        <v>74</v>
-      </c>
-      <c r="X4" t="n">
-        <v>73</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>87</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>81</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>116</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>83</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>59</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>129</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>124</v>
       </c>
     </row>
     <row r="5">

--- a/A 题/result2.xlsx
+++ b/A 题/result2.xlsx
@@ -606,58 +606,58 @@
         <v>23</v>
       </c>
       <c r="G3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>46</v>
+      </c>
+      <c r="V3" t="n">
+        <v>16</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X3" t="n">
         <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" t="n">
-        <v>46</v>
-      </c>
-      <c r="K3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>27</v>
-      </c>
-      <c r="M3" t="n">
-        <v>28</v>
-      </c>
-      <c r="N3" t="n">
-        <v>25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>24</v>
-      </c>
-      <c r="U3" t="n">
-        <v>48</v>
-      </c>
-      <c r="V3" t="n">
-        <v>37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>46</v>
-      </c>
-      <c r="X3" t="n">
-        <v>44</v>
       </c>
       <c r="Y3" t="n">
         <v>50</v>
@@ -1210,16 +1210,16 @@
         <v>83</v>
       </c>
       <c r="P2" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q2" t="n">
         <v>92</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>91</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>92</v>
-      </c>
-      <c r="S2" t="n">
-        <v>93</v>
       </c>
       <c r="T2" t="n">
         <v>94</v>
@@ -1795,10 +1795,10 @@
         <v>23</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>89</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>23</v>
@@ -1869,85 +1869,85 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="O3" t="n">
         <v>54</v>
       </c>
       <c r="P3" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R3" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="AA3" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2089,7 +2089,7 @@
         <v>67</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -2709,10 +2709,10 @@
         <v>102</v>
       </c>
       <c r="AA3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB3" t="n">
         <v>10</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14</v>
       </c>
       <c r="AC3" t="n">
         <v>55</v>
@@ -2724,13 +2724,13 @@
         <v>40</v>
       </c>
       <c r="AF3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH3" t="n">
         <v>47</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>40</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
@@ -2846,10 +2846,10 @@
         <v>73</v>
       </c>
       <c r="V4" t="n">
+        <v>75</v>
+      </c>
+      <c r="W4" t="n">
         <v>74</v>
-      </c>
-      <c r="W4" t="n">
-        <v>75</v>
       </c>
       <c r="X4" t="n">
         <v>52</v>
